--- a/alupar_valuation/alupar_valuation_model.xlsx
+++ b/alupar_valuation/alupar_valuation_model.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Read me" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Dados de origem" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Inputs" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Transmissão" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Geração" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Consolidado" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Valuation" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Sensibilidade" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dados de origem" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inputs" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transmissão" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Geração" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Consolidado" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Valuation" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sensibilidade" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="PxUnit">'Dados de origem'!$C$6</definedName>
@@ -318,13 +318,13 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -347,14 +347,14 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -379,14 +379,14 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -411,14 +411,14 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -458,8 +458,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -485,7 +485,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>15</col>
@@ -500,9 +500,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -800,7 +800,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A31"/>
+  <dimension ref="A1:A33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="118" customWidth="1" min="1" max="1"/>
@@ -860,7 +860,7 @@
     <row r="12" ht="75" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>1. TRANSMISSÃO. A RAP bruta da base operacional é reconstruída a partir da receita líquida regulatória de transmissão do 1T26 anualizada, revertida pela alíquota de deduções. O pipeline é tratado em bloco: o capex de R$ 9,1 bi é distribuído entre 2026 e 2029, e cada real desembolsado passa a gerar RAP dois anos depois, ao yield do último leilão (RAP/capex do Lote 7 = 8,9%). A base atual expira linearmente entre 2042 e 2055; o pipeline roda 30 anos a partir da energização.</t>
+          <t>1. TRANSMISSÃO. A RAP bruta da base operacional é reconstruída a partir da receita líquida regulatória de transmissão do 1T26 anualizada, revertida pela alíquota de deduções. O pipeline é tratado em bloco: o capex de R$ 9,1 bi é distribuído entre 2026 e 2029, e cada real desembolsado passa a gerar RAP dois anos depois, ao yield do último leilão (RAP/capex do Lote 7 = 8,9%). A base atual expira linearmente entre 2030 e 2047 (âncoras: ECTE, EBTE e Aimorés); o pipeline roda 30 anos a partir da energização.</t>
         </is>
       </c>
     </row>
@@ -892,10 +892,10 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="60" customHeight="1">
+    <row r="18" ht="90" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>• O CRONOGRAMA DE VENCIMENTOS É INVENTADO. A base operacional são 31 sistemas com datas de outorga diferentes, e essa lista não estava disponível publicamente na coleta. O decaimento linear entre 2042 e 2055 é uma aproximação grosseira de algo que deveria ser ativo a ativo. É a premissa que mais move o valor no longo prazo. Substitua-a por um cronograma real assim que tiver a lista da ANEEL.</t>
+          <t>• O CRONOGRAMA DE VENCIMENTOS É APROXIMADO, AGORA COM ÂNCORAS REAIS. A base operacional são 31 sistemas com datas de outorga diferentes, e a lista completa não está disponível publicamente. O decaimento linear entre 2030 e 2047 usa as únicas três datas de concessão da Alupar que encontramos publicadas — ECTE (2030), EBTE (2038) e Aimorés (2047) — em vez de um intervalo inventado. Ainda é uma média de três pontos aplicada a 31 ativos, não um cronograma ativo a ativo, e seguem sendo a premissa que mais move o valor no longo prazo. Substitua-a assim que tiver a lista completa da ANEEL.</t>
         </is>
       </c>
     </row>
@@ -941,36 +941,50 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="90" customHeight="1">
+    <row r="26" ht="75" customHeight="1">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>• O MODELO NÃO REPRODUZ O PREÇO DE MERCADO, e não se deve forçá-lo a isso. Com as premissas padrão o DCF dá cerca de R$ 21/unit contra uma cotação de R$ 33,75, e a TIR real implícita fica pouco acima da NTN-B. As linhas "Gap a explicar" na aba Valuation medem exatamente essa diferença. Ela é a pergunta de investimento, não um defeito a ser calibrado: o mercado está pagando por renovação de concessões, leilões além de 2045 ou um custo de capital menor do que os 11,5% reais assumidos aqui. A leitura mais robusta do arquivo é a TIR real implícita, não o preço-alvo — ela não depende de escolher um Ke.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="60" customHeight="1">
+          <t>• A ECONOMIA DE CAPEX DO LOTE 7 FOI REVISADA PARA CIMA. A versão anterior assumia que a Alupar constrói a 80% do capex de referência da ANEEL (20% de economia), uma estimativa de trabalho. A imprensa especializada (ADVFN, jul/2026) noticiou uma economia de ~30% para esse lote especificamente, então o input passou para 70%. Isso melhora o retorno por real investido no pipeline e empurra o valor na direção contrária à da NTN-B — mas é um efeito de segunda ordem perto do impacto da taxa de desconto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="90" customHeight="1">
       <c r="A27" s="3" t="inlineStr">
         <is>
+          <t>• A NTN-B ESTAVA DESATUALIZADA, E ISSO MUDA O RESULTADO MAIS DO QUE QUALQUER OUTRA CORREÇÃO. A versão anterior usava 7,00% real (dado de meados de julho). Em 31-jul-2026 o vértice mais líquido do Tesouro IPCA+ (2035, ~9 anos) pagava 8,33% real — juros longos abriram no trimestre por tensão geopolítica e preocupação fiscal doméstica. Como o fluxo roda até 2080, o efeito de 133 p.p.-base a mais de desconto composto por décadas é enorme: o Ke real vai de 11,5% para 12,83%, e o preço-alvo cai de ~R$ 21 para R$ 11,62/unit — quase pela metade — sem que uma única premissa operacional tenha mudado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="150" customHeight="1">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>• O MODELO NÃO REPRODUZ O PREÇO DE MERCADO, e não se deve forçá-lo a isso. Com as premissas padrão e a NTN-B atualizada, o DCF dá cerca de R$ 11,62/unit contra uma cotação de R$ 32,62 (31-jul-2026) — um gap de ~R$ 21/unit, o dobro do que era antes de corrigir a taxa. Mais revelador: a TIR real implícita no preço atual cai para 4,75% a.a., ABAIXO dos 8,33% da própria NTN-B — quem compra ALUP11 hoje, pelo fluxo deste modelo, aceita um retorno real menor que o do título público que deveria ser seu piso. As linhas "Gap a explicar" na aba Valuation medem essa diferença. Ela é a pergunta de investimento, não um defeito a ser calibrado: o mercado está pagando por renovação de concessões, leilões além de 2045, sinergias ou um custo de capital menor do que os 12,83% reais assumidos aqui — ou o modelo real ainda está com viés pessimista demais na base operacional. A leitura mais robusta do arquivo é a TIR real implícita, não o preço-alvo — ela não depende de escolher um Ke.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="60" customHeight="1">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
           <t>• O MODELO FOI AFERIDO CONTRA TRÊS ÂNCORAS DIVULGADAS, e o resultado está na parte de baixo da aba Consolidado: EBITDA de 2026 a 3,5% do run-rate do 1T26, receita de geração e comercialização a 0,1% da implícita no trimestre, e pico de alavancagem de 3,5x em 2027 contra guidance de 3,9–4,0x em 2028. Recalibre os Inputs se qualquer uma dessas linhas destoar.</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="45" customHeight="1">
-      <c r="A28" s="3" t="inlineStr">
+    <row r="30" ht="45" customHeight="1">
+      <c r="A30" s="3" t="inlineStr">
         <is>
           <t>• OS DADOS DE ORIGEM VÊM DE AGREGADORES E DA IMPRENSA, não dos arquivos da companhia. O acesso direto ao site de RI e aos releases foi bloqueado pela rede na montagem. Confira a aba Dados de origem contra o release oficial antes de usar isto para qualquer coisa que importe.</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>Uso</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="45" customHeight="1">
-      <c r="A31" s="3" t="inlineStr">
+    <row r="33" ht="45" customHeight="1">
+      <c r="A33" s="3" t="inlineStr">
         <is>
           <t>Material de estudo. Não é recomendação de investimento, e os números não foram auditados contra as demonstrações financeiras da companhia. O workbook foi recalculado de ponta a ponta e não contém nenhuma célula de erro, mas isso atesta a aritmética, não as premissas.</t>
         </is>
@@ -1051,7 +1065,7 @@
         </is>
       </c>
       <c r="C6" s="8" t="n">
-        <v>33.75</v>
+        <v>32.62</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
@@ -1060,7 +1074,7 @@
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>Cotação de 15-jul-2026 (agregadores de mercado). Atualize antes de usar.</t>
+          <t>Fechamento de 31-jul-2026 (Status Invest / Dados de Mercado). Atualize antes de usar.</t>
         </is>
       </c>
     </row>
@@ -1596,11 +1610,11 @@
         </is>
       </c>
       <c r="C6" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.0833</v>
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>Taxa livre de risco real. Como a RAP é indexada ao IPCA, o desconto é real e comparável ao título.</t>
+          <t>Taxa livre de risco real. Tesouro IPCA+ 2035 (~9 anos, vértice mais líquido), IPCA+8,33% a.a. em jul/2026 — juros longos abriram no trimestre por aversão a risco externa e preocupação fiscal doméstica. Como a RAP é indexada ao IPCA, o desconto é real e comparável ao título.</t>
         </is>
       </c>
     </row>
@@ -1711,11 +1725,11 @@
         </is>
       </c>
       <c r="C15" s="16" t="n">
-        <v>2042</v>
+        <v>2030</v>
       </c>
       <c r="E15" s="9" t="inlineStr">
         <is>
-          <t>Ano em que a RAP da base operacional começa a expirar.</t>
+          <t>Ano em que a RAP da base operacional começa a expirar. Ancorado em 3 concessões controladas pela Alupar com data pública: ECTE vence em 2030, EBTE em 2038, Aimorés em 2047 — a mais antiga do trio abre a janela.</t>
         </is>
       </c>
     </row>
@@ -1726,11 +1740,11 @@
         </is>
       </c>
       <c r="C16" s="16" t="n">
-        <v>2055</v>
+        <v>2047</v>
       </c>
       <c r="E16" s="9" t="inlineStr">
         <is>
-          <t>Ano em que a última concessão da base atual expira. Entre os dois anos a RAP decai linearmente até zero. É a hipótese mais grosseira do modelo — ver Read me.</t>
+          <t>Ano em que a última concessão da base atual expira. Entre os dois anos a RAP decai linearmente até zero. Mesma âncora de 3 concessões (2030/2038/2047) — ainda uma aproximação linear de algo que é ativo a ativo, mas presa a datas reais em vez de inventada. É a hipótese que mais move o valor no longo prazo — ver Read me.</t>
         </is>
       </c>
     </row>
@@ -1766,11 +1780,11 @@
         </is>
       </c>
       <c r="C20" s="17" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="E20" s="9" t="inlineStr">
         <is>
-          <t>Quanto a companhia efetivamente gasta para cada real do capex de referência do leilão. Construir abaixo da referência é de onde vem boa parte do retorno em transmissão. 0,80 = constrói 20% abaixo. Em 100% o projeto rende apenas o yield nominal do leilão e a expansão vira destruição de valor.</t>
+          <t>Quanto a companhia efetivamente gasta para cada real do capex de referência do leilão. Construir abaixo da referência é de onde vem boa parte do retorno em transmissão. 0,70 = constrói ~30% abaixo, a economia de capex divulgada para o Lote 7 (ADVFN, jul/2026) — mais agressiva que a estimativa inicial de 20%. Em 100% o projeto rende apenas o yield nominal do leilão e a expansão vira destruição de valor.</t>
         </is>
       </c>
     </row>
@@ -14657,27 +14671,27 @@
         </is>
       </c>
       <c r="B23" s="36">
-        <f>IRR(B28:B83,Ke)</f>
+        <f>IRR(B28:B83,0.03)</f>
         <v/>
       </c>
       <c r="C23" s="36">
-        <f>IRR(C28:C83,Ke)</f>
+        <f>IRR(C28:C83,0.03)</f>
         <v/>
       </c>
       <c r="D23" s="36">
-        <f>IRR(D28:D83,Ke)</f>
+        <f>IRR(D28:D83,0.03)</f>
         <v/>
       </c>
       <c r="E23" s="36">
-        <f>IRR(E28:E83,Ke)</f>
+        <f>IRR(E28:E83,0.03)</f>
         <v/>
       </c>
       <c r="F23" s="36">
-        <f>IRR(F28:F83,Ke)</f>
+        <f>IRR(F28:F83,0.03)</f>
         <v/>
       </c>
       <c r="G23" s="36">
-        <f>IRR(G28:G83,Ke)</f>
+        <f>IRR(G28:G83,0.03)</f>
         <v/>
       </c>
     </row>
